--- a/data/trans_orig/P6904-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P6904-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21787</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33995</t>
+          <t>33892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10005</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20744</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34949</t>
+          <t>34555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>52017</t>
+          <t>51560</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8849</t>
+          <t>8952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18828</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19446</t>
+          <t>19903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36514</t>
+          <t>36908</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,65%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27475</t>
+          <t>27520</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45514</t>
+          <t>46139</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,95%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13912</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24960</t>
+          <t>24314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43267</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65485</t>
+          <t>65942</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>62,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44922</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,05%</t>
+          <t>61,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7728</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>19010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>57,44%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39599</t>
+          <t>39142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61817</t>
+          <t>60064</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>58,83%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13435</t>
+          <t>13659</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>25814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,25%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4844</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,46%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>20965</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35882</t>
+          <t>36253</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,14%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10892</t>
+          <t>10801</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23180</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,31%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7938</t>
+          <t>7990</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16880</t>
+          <t>16890</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>22086</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37568</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,06%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17007</t>
+          <t>17455</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32043</t>
+          <t>32603</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14268</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24364</t>
+          <t>25371</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43821</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,08%</t>
+          <t>53,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>25720</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41316</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,84%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8490</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>17621</t>
+          <t>17530</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37208</t>
+          <t>37995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>56665</t>
+          <t>55658</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>68,69%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14174</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>60,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>70,82%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>52,23%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>39,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2965</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>14710</t>
+          <t>14296</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24595</t>
+          <t>24603</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>82,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10526</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22912</t>
+          <t>23692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9924</t>
+          <t>9889</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>16519</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>30343</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18118</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31704</t>
+          <t>31284</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>4205</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>12058</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25814</t>
+          <t>25560</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>40510</t>
+          <t>39384</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34153</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>53015</t>
+          <t>52900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>59,94%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15713</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>55711</t>
+          <t>55180</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77554</t>
+          <t>78108</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,18%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35433</t>
+          <t>35548</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>54295</t>
+          <t>55377</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,06%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>14383</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27822</t>
+          <t>27055</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54429</t>
+          <t>53875</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>76803</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,19%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>57921</t>
+          <t>58026</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78266</t>
+          <t>77224</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23602</t>
+          <t>25031</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>38223</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>88179</t>
+          <t>86779</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>111576</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,31%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30649</t>
+          <t>31691</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>50994</t>
+          <t>50889</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11563</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26184</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>46812</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>70522</t>
+          <t>71922</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,32%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>223693</t>
+          <t>222390</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>268198</t>
+          <t>267606</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>100160</t>
+          <t>98975</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>129872</t>
+          <t>128347</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>333659</t>
+          <t>334291</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>386773</t>
+          <t>387206</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>204107</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>248612</t>
+          <t>249915</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>90249</t>
+          <t>91774</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>119961</t>
+          <t>121146</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>305654</t>
+          <t>305221</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>358768</t>
+          <t>358136</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,81%</t>
+          <t>51,72%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2012 (tasa de respuesta: 98,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16829</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29342</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>23115</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32714</t>
+          <t>33363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49164</t>
+          <t>49346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>49,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>10119</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22665</t>
+          <t>23531</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15266</t>
+          <t>15153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18307</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34757</t>
+          <t>34108</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>50,55%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>29057</t>
+          <t>29053</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44016</t>
+          <t>44022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7827</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19813</t>
+          <t>19757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39280</t>
+          <t>39647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>59087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,0%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12574</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>27533</t>
+          <t>27537</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>48,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14502</t>
+          <t>14558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31544</t>
+          <t>31818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51625</t>
+          <t>51258</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>56,39%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>9790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19645</t>
+          <t>19507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12984</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>5798</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14739</t>
+          <t>15515</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>5370</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13888</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26394</t>
+          <t>26125</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>60,42%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14843</t>
+          <t>15989</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>29041</t>
+          <t>30373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,74%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>10253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29172</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46770</t>
+          <t>47787</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>64,23%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15819</t>
+          <t>14487</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>28871</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,91%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20053</t>
+          <t>19282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27625</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45223</t>
+          <t>44822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>60,25%</t>
         </is>
       </c>
     </row>
@@ -5428,7 +5428,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10310</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>64,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10720</t>
+          <t>10723</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16390</t>
+          <t>16370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>25399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,27%</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8072</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2431</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>11460</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>17483</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30636</t>
+          <t>30530</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7845</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21226</t>
+          <t>21548</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>36881</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,98%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>12744</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>25897</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7339</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>14198</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22444</t>
+          <t>21683</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37338</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,21%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14085</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29135</t>
+          <t>29822</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>55,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>33012</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39197</t>
+          <t>38377</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>59701</t>
+          <t>58084</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>58,15%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24374</t>
+          <t>23687</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>39424</t>
+          <t>38991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12837</t>
+          <t>13368</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26835</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40189</t>
+          <t>41806</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60693</t>
+          <t>61513</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,58%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12713</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25985</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23035</t>
+          <t>22568</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>73,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>27932</t>
+          <t>27213</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>45759</t>
+          <t>45807</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20163</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>8104</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19675</t>
+          <t>19501</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>31061</t>
+          <t>31013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>48888</t>
+          <t>49607</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>160143</t>
+          <t>159921</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>197915</t>
+          <t>196372</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>94801</t>
+          <t>96046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>124703</t>
+          <t>125458</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>264194</t>
+          <t>265561</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>312849</t>
+          <t>316514</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,71%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>127540</t>
+          <t>129083</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>165312</t>
+          <t>165534</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,79%</t>
+          <t>50,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>88203</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118860</t>
+          <t>117615</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>226267</t>
+          <t>222602</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>274922</t>
+          <t>273555</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16105</t>
+          <t>16585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>31667</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22135</t>
+          <t>21567</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33679</t>
+          <t>33437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>81,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41859</t>
+          <t>42192</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62384</t>
+          <t>62099</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>62,44%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26640</t>
+          <t>26910</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42472</t>
+          <t>41992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18749</t>
+          <t>19317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37077</t>
+          <t>37362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57602</t>
+          <t>57269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>53634</t>
+          <t>53355</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69256</t>
+          <t>69119</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27261</t>
+          <t>27038</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38493</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>84916</t>
+          <t>85263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>104504</t>
+          <t>105120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,77%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13530</t>
+          <t>13667</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29152</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15436</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20979</t>
+          <t>20363</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>40567</t>
+          <t>40220</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>20319</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10825</t>
+          <t>10788</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20037</t>
+          <t>19920</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30039</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,36%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,99%</t>
+          <t>87,57%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>935</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7581</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1676</t>
+          <t>1713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8496</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3716</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13718</t>
+          <t>13835</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,99%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>16171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>26752</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>13567</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24194</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34046</t>
+          <t>34155</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>48947</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5440</t>
+          <t>5713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>16294</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16420</t>
+          <t>16368</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>28245</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,44%</t>
+          <t>45,26%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4131</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1948</t>
+          <t>1856</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17516</t>
+          <t>17617</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3823</t>
+          <t>3915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3125</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12075</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4001</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12391</t>
+          <t>12865</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>57,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3266</t>
+          <t>3294</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -9144,7 +9144,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19907</t>
+          <t>19780</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10043</t>
+          <t>9569</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18433</t>
+          <t>18614</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4161</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9262,7 +9262,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9953</t>
+          <t>10080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,02%</t>
+          <t>69,64%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42506</t>
+          <t>42028</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59652</t>
+          <t>59941</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24917</t>
+          <t>25001</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40656</t>
+          <t>40516</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,75%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>72327</t>
+          <t>72954</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95027</t>
+          <t>96196</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>53,97%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>18690</t>
+          <t>18401</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>36314</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>30681</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,25%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>38997</t>
+          <t>37828</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61697</t>
+          <t>61070</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>46,03%</t>
+          <t>45,57%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9098</t>
+          <t>8921</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21116</t>
+          <t>21411</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15707</t>
+          <t>16160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>18558</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34521</t>
+          <t>34482</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,83%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>30353</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5240</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14980</t>
+          <t>14961</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26192</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>42429</t>
+          <t>42116</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>69,41%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>189336</t>
+          <t>189315</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>227259</t>
+          <t>228223</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>131567</t>
+          <t>131790</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>159313</t>
+          <t>158949</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>60,83%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,49%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>330461</t>
+          <t>331123</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>377016</t>
+          <t>377794</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>122742</t>
+          <t>121778</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>160665</t>
+          <t>160686</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>56985</t>
+          <t>57349</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>84731</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>189283</t>
+          <t>188505</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>235838</t>
+          <t>235176</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,65%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene dolores musculares en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18782</t>
+          <t>18677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>8498</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15032</t>
+          <t>15165</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32509</t>
+          <t>32480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5287</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,5%</t>
+          <t>65,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>590</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>7257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19110</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17373</t>
+          <t>18291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>34861</t>
+          <t>35173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>76,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30130</t>
+          <t>29902</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39830</t>
+          <t>40196</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60396</t>
+          <t>61072</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11419</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>28907</t>
+          <t>27989</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>15313</t>
+          <t>15541</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27359</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31327</t>
+          <t>30651</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51893</t>
+          <t>51527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,58%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18746</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32343</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>31251</t>
+          <t>31252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,7 +11438,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42321</t>
+          <t>42571</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59801</t>
+          <t>59358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>44,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17685</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30749</t>
+          <t>31004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14675</t>
+          <t>14674</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26182</t>
+          <t>25744</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35621</t>
+          <t>36064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,39%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22152</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36065</t>
+          <t>36061</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>60747</t>
+          <t>60957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78158</t>
+          <t>77496</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88910</t>
+          <t>88646</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113456</t>
+          <t>113407</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,48%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4292</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18201</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2494</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32095</t>
+          <t>32359</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11919</t>
+          <t>11855</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2807</t>
+          <t>3020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7186</t>
+          <t>7273</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>9279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>17339</t>
+          <t>17576</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,15%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12950</t>
+          <t>12791</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>7966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11404</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19752</t>
+          <t>19464</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>67,72%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24148</t>
+          <t>24040</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12754</t>
+          <t>12622</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>21534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>29593</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>43206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7468</t>
+          <t>7576</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>17478</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17461</t>
+          <t>17593</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>18684</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32142</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,14%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32771</t>
+          <t>32718</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52734</t>
+          <t>53239</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,55%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75720</t>
+          <t>75440</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99187</t>
+          <t>99126</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23367</t>
+          <t>23453</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>40407</t>
+          <t>40460</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,22%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17793</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>32056</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44518</t>
+          <t>44579</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67985</t>
+          <t>68265</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35745</t>
+          <t>35869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>48575</t>
+          <t>48708</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>22102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>38274</t>
+          <t>37906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>69,96%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>61528</t>
+          <t>61778</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81531</t>
+          <t>81212</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>72,86%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>8049</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21012</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32542</t>
+          <t>32608</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49939</t>
+          <t>49689</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>44,8%</t>
+          <t>44,58%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>188867</t>
+          <t>188962</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>227692</t>
+          <t>227403</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,98%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>210530</t>
+          <t>211471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>266559</t>
+          <t>267993</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>409751</t>
+          <t>410195</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>480048</t>
+          <t>477653</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>111813</t>
+          <t>112102</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>150638</t>
+          <t>150543</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>87656</t>
+          <t>86222</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>143685</t>
+          <t>142744</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>213672</t>
+          <t>216067</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>283969</t>
+          <t>283525</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,87%</t>
         </is>
       </c>
     </row>
